--- a/data/trans_orig/IP19C01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19C01-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24913</t>
+          <t>25176</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35286</t>
+          <t>35666</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25070</t>
+          <t>25492</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34492</t>
+          <t>34744</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53229</t>
+          <t>52915</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67670</t>
+          <t>66940</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>74,53%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11640</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22013</t>
+          <t>21750</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17821</t>
+          <t>17399</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22146</t>
+          <t>22876</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36587</t>
+          <t>36901</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,08%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>132850</t>
+          <t>131115</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>155983</t>
+          <t>154664</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>162664</t>
+          <t>162899</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>185344</t>
+          <t>185680</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>301964</t>
+          <t>300910</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>335510</t>
+          <t>334186</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,5%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72339</t>
+          <t>73658</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>95472</t>
+          <t>97207</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60379</t>
+          <t>60043</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83059</t>
+          <t>82824</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>138535</t>
+          <t>139859</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>172081</t>
+          <t>173135</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51330</t>
+          <t>51501</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63648</t>
+          <t>63546</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46515</t>
+          <t>46782</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59318</t>
+          <t>58916</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102920</t>
+          <t>101877</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119525</t>
+          <t>119386</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,23%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12035</t>
+          <t>12137</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24353</t>
+          <t>24182</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13799</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26602</t>
+          <t>26335</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29275</t>
+          <t>29414</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45880</t>
+          <t>46923</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,53%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>217367</t>
+          <t>216587</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>245325</t>
+          <t>244928</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>244823</t>
+          <t>244598</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>271292</t>
+          <t>271064</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>470225</t>
+          <t>470844</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>511548</t>
+          <t>509320</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,47%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>105605</t>
+          <t>106002</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>133563</t>
+          <t>134343</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90439</t>
+          <t>90667</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>116908</t>
+          <t>117133</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>201113</t>
+          <t>203341</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>242436</t>
+          <t>241817</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29992</t>
+          <t>29400</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39746</t>
+          <t>39569</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26437</t>
+          <t>26348</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36192</t>
+          <t>36151</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59887</t>
+          <t>59543</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73765</t>
+          <t>73520</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,85%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17972</t>
+          <t>18564</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16526</t>
+          <t>16615</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17163</t>
+          <t>17408</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31041</t>
+          <t>31385</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>141858</t>
+          <t>142504</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>164937</t>
+          <t>165908</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>167051</t>
+          <t>165685</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>188795</t>
+          <t>188765</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>316269</t>
+          <t>315401</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>348880</t>
+          <t>347833</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,83%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57572</t>
+          <t>56601</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80651</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53513</t>
+          <t>53543</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>75257</t>
+          <t>76623</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>115937</t>
+          <t>116984</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>148548</t>
+          <t>149416</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60329</t>
+          <t>60454</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73204</t>
+          <t>73969</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63072</t>
+          <t>62509</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73687</t>
+          <t>73458</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126969</t>
+          <t>126886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143329</t>
+          <t>143521</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,6%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12344</t>
+          <t>11579</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25219</t>
+          <t>25094</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8667</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19053</t>
+          <t>19616</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24344</t>
+          <t>24152</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40704</t>
+          <t>40787</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>243057</t>
+          <t>243040</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>269024</t>
+          <t>270963</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>264985</t>
+          <t>264906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>292453</t>
+          <t>292529</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>516222</t>
+          <t>516752</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>555101</t>
+          <t>553917</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,57%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86997</t>
+          <t>85058</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>112964</t>
+          <t>112981</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74944</t>
+          <t>74868</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102412</t>
+          <t>102491</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>168317</t>
+          <t>169501</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>207196</t>
+          <t>206666</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>9794</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18146</t>
+          <t>17601</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15946</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23934</t>
+          <t>23744</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28932</t>
+          <t>29297</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39734</t>
+          <t>39617</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,52%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12572</t>
+          <t>13248</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12788</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>22480</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,42%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>173397</t>
+          <t>172032</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>195348</t>
+          <t>195686</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>189279</t>
+          <t>188461</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>210853</t>
+          <t>209824</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>368159</t>
+          <t>367521</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>399032</t>
+          <t>400682</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,81%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58115</t>
+          <t>57777</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80066</t>
+          <t>81431</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44117</t>
+          <t>45146</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65691</t>
+          <t>66509</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109401</t>
+          <t>107751</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>140274</t>
+          <t>140912</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,71%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63539</t>
+          <t>62814</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75993</t>
+          <t>75438</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54639</t>
+          <t>55468</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69351</t>
+          <t>69661</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121573</t>
+          <t>121440</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140800</t>
+          <t>140745</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,87%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12525</t>
+          <t>13080</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24979</t>
+          <t>25704</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18347</t>
+          <t>18037</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33059</t>
+          <t>32230</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35416</t>
+          <t>35471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54643</t>
+          <t>54776</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,08%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>253328</t>
+          <t>254511</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>282120</t>
+          <t>283010</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>267518</t>
+          <t>268115</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>294469</t>
+          <t>294193</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>529969</t>
+          <t>530285</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>569772</t>
+          <t>568634</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,22%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82904</t>
+          <t>82014</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111696</t>
+          <t>110513</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76933</t>
+          <t>77209</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>103884</t>
+          <t>103287</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>166653</t>
+          <t>167791</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>206456</t>
+          <t>206140</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14708</t>
+          <t>14541</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27219</t>
+          <t>26950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17656</t>
+          <t>16940</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24059</t>
+          <t>24188</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35323</t>
+          <t>34798</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49851</t>
+          <t>49723</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,05%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15022</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19891</t>
+          <t>20416</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,98%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>209014</t>
+          <t>207797</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>230059</t>
+          <t>229252</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>240049</t>
+          <t>242516</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>272746</t>
+          <t>272953</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>458963</t>
+          <t>459494</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>496239</t>
+          <t>497396</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,05%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31768</t>
+          <t>32575</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52813</t>
+          <t>54030</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50269</t>
+          <t>50062</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82966</t>
+          <t>80499</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>88603</t>
+          <t>87446</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>125879</t>
+          <t>125348</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69338</t>
+          <t>69801</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83978</t>
+          <t>84003</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110327</t>
+          <t>110958</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>124945</t>
+          <t>125384</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>184429</t>
+          <t>185313</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205449</t>
+          <t>205741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,17%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16098</t>
+          <t>16073</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30738</t>
+          <t>30275</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11000</t>
+          <t>10561</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25618</t>
+          <t>24987</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30572</t>
+          <t>30280</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51592</t>
+          <t>50708</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>305727</t>
+          <t>304341</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>332886</t>
+          <t>332207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>379470</t>
+          <t>381145</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>414420</t>
+          <t>414784</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>694445</t>
+          <t>696742</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>738683</t>
+          <t>739765</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,44%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58747</t>
+          <t>59426</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>85906</t>
+          <t>87292</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70024</t>
+          <t>69660</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>104974</t>
+          <t>103299</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>137393</t>
+          <t>136311</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>181631</t>
+          <t>179334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19C01-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,67 +728,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>30256</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>25172</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34588</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>70,54%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>58,69%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>80,64%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>30345</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25176</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>35666</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>24810</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>35261</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>64,67%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>53,65%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>76,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>30256</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>25492</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>34744</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>70,54%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52915</t>
+          <t>53086</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66940</t>
+          <t>67046</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,65%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12635</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8303</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17719</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>29,46%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>19,36%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>41,31%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>16581</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11260</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21750</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11665</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>22116</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>35,33%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>24,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>46,35%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12635</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>8147</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17399</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>29,46%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22876</t>
+          <t>22770</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36901</t>
+          <t>36730</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>174257</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>162097</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>185480</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>70,92%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>65,97%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>75,48%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>144179</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>131115</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>154664</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>131816</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>155148</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>63,15%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>57,43%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>67,74%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>174257</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>162899</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>185680</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>70,92%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>300910</t>
+          <t>301948</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>334186</t>
+          <t>334338</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,53%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>71466</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>60243</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>83626</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>29,08%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>24,52%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>34,03%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>84143</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>73658</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>97207</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>73174</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>96506</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>36,85%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>32,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>42,57%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>71466</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>60043</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>82824</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>29,08%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>139859</t>
+          <t>139707</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>173135</t>
+          <t>172097</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,3%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>343</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>53707</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>58992</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>73,45%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>63,63%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>80,68%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>57694</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>51501</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>63546</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>51083</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>63020</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>76,23%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>68,05%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>83,96%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>53707</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>46782</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>58916</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>73,45%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101877</t>
+          <t>102271</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119386</t>
+          <t>119844</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,54%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>19410</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14125</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>26592</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>26,55%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>19,32%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>36,37%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>17989</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12137</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>24182</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12663</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>24600</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>23,77%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>16,04%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>31,95%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>19410</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>14201</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>26335</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>26,55%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29414</t>
+          <t>28956</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46923</t>
+          <t>46529</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -1640,52 +1640,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>75683</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>258220</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>244477</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>272001</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>71,38%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>67,59%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>75,19%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>232218</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>216587</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>244928</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>215484</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>244818</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>66,17%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>61,72%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>69,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>258220</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>244598</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>271064</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>71,38%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>470844</t>
+          <t>469582</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>509320</t>
+          <t>510472</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,63%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>103511</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>89730</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>117254</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>28,62%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>24,81%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>32,41%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>118712</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>106002</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>134343</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>106112</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>135446</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>33,83%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>30,21%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>38,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>103511</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>90667</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>117133</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>28,62%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>203341</t>
+          <t>202189</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>241817</t>
+          <t>243079</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>31866</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26190</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35923</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>74,17%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>60,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>83,61%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>35372</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>29400</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>39569</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>30433</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>39876</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>73,75%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>61,3%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>82,5%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>31866</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>26348</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>36151</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>74,17%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59543</t>
+          <t>59731</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73520</t>
+          <t>73362</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,68%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11097</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7040</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16773</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>25,83%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,39%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>39,04%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>12592</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8395</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18564</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8088</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17531</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>26,25%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,5%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>38,7%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>11097</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6812</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>16615</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>25,83%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17408</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31385</t>
+          <t>31197</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,31%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>47964</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>42963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>178006</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>165343</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>189566</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>73,46%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>68,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>78,23%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>154504</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>142504</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>165908</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>143668</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>165755</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>69,44%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>64,04%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>74,56%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>178006</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>165685</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>188765</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>73,46%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>315401</t>
+          <t>313860</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>347833</t>
+          <t>347803</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>64302</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>52742</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>76965</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>26,54%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,77%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>31,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>68005</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>56601</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>80005</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>56754</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>78841</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>30,56%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25,44%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>35,96%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>64302</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>53543</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>76623</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>26,54%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>116984</t>
+          <t>117014</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149416</t>
+          <t>150957</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,48%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>242308</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>242308</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>242308</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>318</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>222509</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>222509</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>222509</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>242308</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>242308</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>242308</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>69259</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>62815</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>73983</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>84,33%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>76,49%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>90,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>66916</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>60454</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>73969</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>59779</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>72635</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>78,22%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>70,67%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>86,46%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>69259</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>62509</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>73458</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>84,33%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126886</t>
+          <t>126905</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143521</t>
+          <t>143875</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12866</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8142</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>19310</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>15,67%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>9,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>23,51%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>18632</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11579</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>25094</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12913</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>25769</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>21,78%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>13,54%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>29,33%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>12866</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>8667</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>19616</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>15,67%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24152</t>
+          <t>23798</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40787</t>
+          <t>40768</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>279132</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>264423</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>291726</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>75,98%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>71,97%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>79,4%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>363</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>256792</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>243040</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>270963</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>241589</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>269703</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>72,13%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>68,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>76,11%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>279132</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>264906</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>292529</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>75,98%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>516752</t>
+          <t>516958</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>553917</t>
+          <t>554768</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,69%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>88265</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>75671</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>102974</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>24,02%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>20,6%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>28,03%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>99229</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>85058</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>112981</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>86318</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>114432</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>27,87%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>23,89%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>31,73%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>88265</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>74868</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>102491</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>24,02%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>169501</t>
+          <t>168650</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>206666</t>
+          <t>206460</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>367397</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>367397</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>367397</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>507</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>356021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>356021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>356021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>367397</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>367397</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>367397</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19964</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15783</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23854</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>69,48%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>54,93%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>83,02%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>14589</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9794</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17601</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>18275</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>63,32%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,5%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>76,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>19964</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>15618</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>23744</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>69,48%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29297</t>
+          <t>28440</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39617</t>
+          <t>39599</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,48%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8770</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4880</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12951</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>30,52%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>45,07%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>8453</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5441</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13248</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4767</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12739</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>36,68%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>23,61%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>57,5%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8770</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4990</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>13116</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>30,52%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22480</t>
+          <t>23337</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>45,07%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28734</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28734</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28734</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>23042</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>23042</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>23042</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28734</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28734</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28734</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>199704</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>188103</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>209701</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>78,32%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>73,77%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>82,25%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>184292</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>172032</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>195686</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>171300</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>195880</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>72,71%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>67,87%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>77,2%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>199704</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>188461</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>209824</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>78,32%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>367521</t>
+          <t>367957</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>400682</t>
+          <t>399245</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,52%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>55266</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>45269</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>66867</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>21,68%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>26,23%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>69171</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>57777</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>81431</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>57583</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>82163</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>27,29%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>22,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>32,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>55266</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>45146</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>66509</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>21,68%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>107751</t>
+          <t>109188</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>140912</t>
+          <t>140476</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>254970</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>254970</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>254970</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>371</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253463</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253463</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253463</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>254970</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>254970</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>254970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>62306</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>55272</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>69053</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>71,05%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>63,03%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>78,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>69686</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>62814</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>75438</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>63015</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>75529</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>78,72%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>70,96%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>85,22%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>62306</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>55468</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>69661</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>71,05%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121440</t>
+          <t>121382</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140745</t>
+          <t>139832</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,35%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25392</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18645</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>32426</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>28,95%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>21,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>36,97%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>18832</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>13080</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>25704</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12989</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>25503</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>21,28%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>14,78%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>29,04%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>25392</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>18037</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>32230</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>28,95%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35471</t>
+          <t>36384</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54776</t>
+          <t>54834</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>88518</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>88518</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>88518</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>281974</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>268126</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>295931</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>75,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>72,19%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>79,68%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>386</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>268568</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>254511</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>283010</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>254062</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>282940</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>73,58%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>69,72%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>77,53%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>281974</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>268115</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>294193</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>75,92%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>530285</t>
+          <t>530895</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>568634</t>
+          <t>569710</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,36%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>89428</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>75471</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>103276</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>24,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>27,81%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>96456</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>82014</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>110513</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>82084</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>110962</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>26,42%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>22,47%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>30,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>89428</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>77209</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>103287</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>24,08%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>167791</t>
+          <t>166715</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>206140</t>
+          <t>205530</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>371402</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>371402</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>371402</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>530</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>365024</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>365024</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>365024</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>371402</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>371402</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>371402</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20575</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16440</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23137</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>84,71%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>67,68%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>95,25%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>22645</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14541</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26950</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>76,17%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>48,91%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>90,65%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21672</t>
+          <t>21969</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16940</t>
+          <t>18186</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24188</t>
+          <t>24628</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>44317</t>
+          <t>42543</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34798</t>
+          <t>37377</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49723</t>
+          <t>46686</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>91,66%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3715</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1153</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7850</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>15,29%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>32,32%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7085</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2780</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15189</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>23,83%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,35%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>51,09%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8544</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>10897</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20416</t>
+          <t>13556</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>248656</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>232862</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>260823</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>80,33%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>75,23%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>84,26%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>220107</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>207797</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>229252</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>84,07%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>79,36%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>87,56%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>258685</t>
+          <t>222638</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>242516</t>
+          <t>211681</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>272953</t>
+          <t>232266</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>478791</t>
+          <t>471294</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>459494</t>
+          <t>451431</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>497396</t>
+          <t>489162</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,98%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>60889</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>48722</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>76683</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>19,67%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>15,74%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>24,77%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>41720</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>32575</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>54030</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>15,93%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,44%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>20,64%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>64330</t>
+          <t>43414</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50062</t>
+          <t>33786</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80499</t>
+          <t>54371</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>106051</t>
+          <t>104303</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87446</t>
+          <t>86435</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>125348</t>
+          <t>124166</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>367</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>111427</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>103865</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>117273</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>87,56%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>81,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>92,15%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>77115</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>69801</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>84003</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>77,06%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>69,75%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>83,94%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>79803</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110958</t>
+          <t>71205</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125384</t>
+          <t>86860</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>196029</t>
+          <t>191229</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>185313</t>
+          <t>179967</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205741</t>
+          <t>200284</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>86,76%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15833</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23395</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>12,44%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>18,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>22961</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>16073</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>30275</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>22,94%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>16,06%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>30,25%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>23780</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10561</t>
+          <t>16723</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24987</t>
+          <t>32378</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>39992</t>
+          <t>39613</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30280</t>
+          <t>30558</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50708</t>
+          <t>50875</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>380658</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>362215</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>394644</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>82,56%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>78,56%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>85,59%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>460</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>319866</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>304341</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>332207</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>81,67%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>77,71%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>84,83%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>399272</t>
+          <t>324410</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>381145</t>
+          <t>310839</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>414784</t>
+          <t>337298</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>719137</t>
+          <t>705067</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>696742</t>
+          <t>684521</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>739765</t>
+          <t>725196</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,58%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>80437</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>66451</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>98880</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>17,44%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>14,41%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>21,44%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>71767</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>59426</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>87292</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>18,33%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15,17%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>22,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>85172</t>
+          <t>71868</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69660</t>
+          <t>58980</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>103299</t>
+          <t>85439</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>156939</t>
+          <t>152305</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>136311</t>
+          <t>132176</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>179334</t>
+          <t>172851</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
